--- a/sr_past_runs.xlsx
+++ b/sr_past_runs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\reionisation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89797CCF-BFF9-43B1-A318-15290B542DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97669F9-7322-44D5-8C3B-F1C3E895DAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="2265" windowWidth="32565" windowHeight="15345" xr2:uid="{9831A600-CFBA-4EAE-B6C2-4EAF59100770}"/>
+    <workbookView xWindow="720" yWindow="3975" windowWidth="37155" windowHeight="15345" xr2:uid="{9831A600-CFBA-4EAE-B6C2-4EAF59100770}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>Condition</t>
   </si>
@@ -65,9 +65,6 @@
     <t>x6*(-0.18702345) - 0.41378346*(x1 + x3) - 4.7948303</t>
   </si>
   <si>
-    <t>batch_size: 4096, operators: {+, - , *, /, pow}, nan_indices:{gas_mass = 0}; pops: 50; nits: 500; maxd: 10</t>
-  </si>
-  <si>
     <t>-0.4313908*x6 + x7*0.5631834 - 4.9753256 - 4.3971167*(x1 + x3 + x7 + 10**(-0.25213522/10**x1))/(10**x0/x7 - x6)</t>
   </si>
   <si>
@@ -84,13 +81,190 @@
   </si>
   <si>
     <t>x6*(-0.18653251) + (x7 - (x1 + x3))/2.706797</t>
+  </si>
+  <si>
+    <t>(x6 - x7 + (10**x0/x7 + x3)*1.5256882 + 10.7244215)/(10**(10**(x6 - (x0 + x7))/((x7/0.3744162))) + x1 - 1*5.167374)</t>
+  </si>
+  <si>
+    <t>(x3*2.1257453 + x6 + 25.149431)/(x1 - 5.138412)</t>
+  </si>
+  <si>
+    <t>(-(-x6 + (x1/0.77687585 + x2 + x3 + x6)*4.281301) - 18.006355)*(x1*0.012263798 - 1*(-0.55307573) + (x2 - 0.4318432)/x6) - 2.092198</t>
+  </si>
+  <si>
+    <t>x6*(-0.19080333) + (x1 + x3)*(-0.4058449) - 4.86033</t>
+  </si>
+  <si>
+    <t>10**((x0 - x1)*0.4374994) + 12.808413 - (-1)*886.2438/(x0 + x3*0.87922525 + x6 + (x0 - x1)*0.500002 - 29.724436) - 59.362873/x6</t>
+  </si>
+  <si>
+    <t>x6*(-0.3341801 + 10.137713/(6.4719343 - (x1 + x3 + x6)))</t>
+  </si>
+  <si>
+    <t>10**((x1 + x3*0.83325577 + x6 + 10.012582)/(-(10**((x0 - 0.8151816*x1)*0.7508107) + x7) - 1.2598606))*(x6*0.70617914 + 4.7878804)</t>
+  </si>
+  <si>
+    <t>10**((x1 + x3 + x6 + 7.7603383)*0.08835787)*(x6 + 6.529851)</t>
+  </si>
+  <si>
+    <t>(-x6 - 28.008947)/(-x1 - x3 + 6.585298)</t>
+  </si>
+  <si>
+    <t>(-x6 + (10**(x0 - x1) - x3 + x7)*1.1810449 - 1*9.335302)/(3.4689515 - (x0 - 1*0.6494573)*(x3 + x7*x7/x6)/x6)</t>
+  </si>
+  <si>
+    <t>(-0.0044814274*(x1 + x3)*(-x6 - 8.335698) - 0.056805953)*(x1 + x1 + x1 - (-x0 - 3.0095072)*(x6 - x7) + 19.992159) - 1.181969</t>
+  </si>
+  <si>
+    <t>-0.36822888*(x1 + x3) + (x6 - x7)*(-0.19652548) - 1*2.4164844</t>
+  </si>
+  <si>
+    <t>(-(x3 + x3 + x6) - 24.905352)/(4.9896603 - x1)</t>
+  </si>
+  <si>
+    <t>(10**(x2 + x3/(x2 - 0.900037) + x6/1.9091616) - (x2 - (-1.2554437)*x3 + x6 + 13.639154))*1.3927174/(3.773693 - x1)</t>
+  </si>
+  <si>
+    <t>f_esc; batch_size: 4096, operators: {+, - , *, /, pow}, nan_indices:{gas_mass = 0}; pops: 100; pop_size: 100; nits: 100; maxd: 8</t>
+  </si>
+  <si>
+    <t>f_esc - basic; batch_size: 4096, operators: {+, - , *, /, pow}, nan_indices:{gas_mass = 0}; pops: 100; pop_size: 100; nits: 100; maxd: 8</t>
+  </si>
+  <si>
+    <t>f_esc; batch_size: 4096, operators: {+, - , *, /, pow}, nan_indices:{gas_mass = 0}; pops: 50; nits: 500; maxd: 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> x10 - 1*2.3013167 - (x0 + x3)*(x3 - (x1 - 1*(-9.485352)))/x2</t>
+  </si>
+  <si>
+    <t>(-(0.048013818 + x0*(-0.327294)) + ((-x0 + x10)*2.3296196 - (-x0 + x3))*(-x1/x2 + x3*0.09635826 - 0.72503096))*1.0919769</t>
+  </si>
+  <si>
+    <t>-1.3186703 + (x0 + x3)*(x1*(x10 + x5)/(-2.097765) + (-x0 + (-x1 + x3)*(x3 - 8.984387))*(-0.13514164))/(10**x10 + 9.032199)</t>
+  </si>
+  <si>
+    <t>(x0 + x3)*(x1*(x10 + x5)/(-22.354944) + x3*(-0.08273085) + 0.73757446) - 1*1.2365417</t>
+  </si>
+  <si>
+    <t>x3*(x3*(-x10 + x3)*(-0.004943128) + 0.24001968) - (-4.170482)*x5/(-(-0.1697825)*x0*(-10**x10 + x0) - 11.991589/x1)</t>
+  </si>
+  <si>
+    <t>(x7 / ((-1.8125479 - (x1 + -6.968299)) + ((((x6 + -3.2798638) + (x1 - x0)) - x7) * ((x3 + (x6 - x7)) * 0.10350539)))) + (x3 * -0.120083764)</t>
+  </si>
+  <si>
+    <t>(-2.4667075 / (x3 + ((x1 / 0.39542353) + x7))) * (pow10((-1.3311294 / pow10(x6 - x7)) + 0.504304) + (x7 - (x3 + ((x6 - x7) * 1.1852814))))</t>
+  </si>
+  <si>
+    <t>(((x3 + x1) * -0.4080511) - (x6 * 0.19026698)) + -4.8429546</t>
+  </si>
+  <si>
+    <t>(0.4266226 - ((((x2 - (x3 * -1.7626185)) * pow10(x6 / x2)) + -0.11479346) * (x6 + (x2 - (-7.987407 - x1))))) * ((-4.8860164 - x3) - x1)</t>
+  </si>
+  <si>
+    <t>(-4.8724027 - (x3 + x1)) * (0.8927747 - (x6 * -0.032352637))</t>
+  </si>
+  <si>
+    <t>(((x1 + x3) * -0.41002434) - (x6 * 0.18719314)) - 4.7952743</t>
+  </si>
+  <si>
+    <t>(pow10(x1 * 0.110406995) * ((x6 * 0.23341626) + 5.6049247)) * (((x1 + x6) * (x3 * 0.014604943)) + ((-0.07885185 * x2) + -0.39000753))</t>
+  </si>
+  <si>
+    <t>(((x1 + x3) * -0.41126016) + -4.7839394) - (x6 * 0.18618326)</t>
+  </si>
+  <si>
+    <t>((x1 * -0.35489285) + ((x3 * -0.29096508) + -9.236683)) + (pow10(-5.1569176 / x6) + ((x6 * 4.856185) / (x7 + -1.8638078)))</t>
+  </si>
+  <si>
+    <t>((x1 + x3) * -0.41141808) - ((x6 * 0.18159461) + 4.7165923)</t>
+  </si>
+  <si>
+    <t>(x1 + x10 - x3 + x5)*0.59097075 + 5.4104776</t>
+  </si>
+  <si>
+    <t>x1 + 0.911209 - (-1)*0.4209733*(-x3*(x3 - 1*4.1609273) + (10**(3.9622607/x3) + x1*x2)*(x0*x1*(-0.092219494) - x10))/x2</t>
+  </si>
+  <si>
+    <t>x3*x3*(x1*(0.012593086 + x10*(-0.007368667)) - 0.017966434), MSE: 0.43645677</t>
+  </si>
+  <si>
+    <t>(-x1 - (x5 - (-x10 + x3)) - 9.125574)*(-0.58692515)</t>
+  </si>
+  <si>
+    <t>(-x1 - (x1 - x3/0.78961957) - 11.375817)*(x1*x0*0.028314717 - 1.0093898 - (x10 + 0.3746691 + x5/x5)/x5) - 1*1.3972892</t>
+  </si>
+  <si>
+    <t>(Changed knee point selection from an incremental to a curvature method)</t>
+  </si>
+  <si>
+    <t>f_esc - basic(obvs); batch_size: 4096, operators: {+, - , *, /, pow}, nan_indices:{gas_mass = 0}; pops: 100; pop_size: 100; nits: 100; maxd: 5</t>
+  </si>
+  <si>
+    <t>-(x0 + x0/x4 + x3)/(5.8824654 - (-1.0231586)*x2) + (x1 + x4)/(((x2*0.021411086))*(x0*x1 + x1 + x2))</t>
+  </si>
+  <si>
+    <t>x1*(x0 + 6.5165753)/x2 - 1.3316052</t>
+  </si>
+  <si>
+    <t>-x1*(-x0 - 6.5118675)/x2 - 1.3337731</t>
+  </si>
+  <si>
+    <t>-x0*(x2 - 4.29261)/x3 + x3*(-0.72456443)/(x2 + 2.0369523) - (-x0 - 5.4743114)*(x1 + x4)/(-x0 + x1 + x2)</t>
+  </si>
+  <si>
+    <t>-0.032822046*x0*(x1*x1 + 3.742748) + x1*5.757454/x2 - 1.4322108</t>
+  </si>
+  <si>
+    <t>x2*(-0.0031112726)*x0*x2 + x1*8.019154/(x2 + 2.4231803) - (x1*0.032454375*x1*x0 + x4*(-0.26299196) + 1.6324205)</t>
+  </si>
+  <si>
+    <t>f_esc(obvs); batch_size: 4096, operators: {+, - , *, /, pow}, nan_indices:{gas_mass = 0}; pops: 100; pop_size: 100; nits: 100; maxd: 5</t>
+  </si>
+  <si>
+    <t>10**(10**(x2*x5)/(x1 - 1.1787784) + 1.8602536/(10**x1 + x3)) + x1/(-0.9829948) - 5.7550254 + (-x3 + x5)/(x1 - 1*2.2239733)</t>
+  </si>
+  <si>
+    <t>-13.715186/(x1*x1 - x2 + x3 - 1*1.6369987)</t>
+  </si>
+  <si>
+    <t>((x1 - x4)*3.440473 - 14.156448)/(-x2 + x3)</t>
+  </si>
+  <si>
+    <t>(10**(x1 - (-1.1056429)*x2/6.18954749770172 - 0.4467055) - x4)*0.37458968 + (-10**(x4*0.31822243)*x1 - x2 - 16.203884)/(-x2 + x3)</t>
+  </si>
+  <si>
+    <t>10**(x1 - 1.0762637) - 0.41431144*x4 + (-x2 + x8)/(x3 - 1*1.1837075)</t>
+  </si>
+  <si>
+    <t>10**(x1 - 0.9461905) - 0.110177785*x1*x4*(x4 + 0.7541851 + 2.576837/x1) + (-x2 + x8)/(x3 - 1*1.4293679)</t>
+  </si>
+  <si>
+    <t>10**(x1 - 1.0619957) - 0.50004286*x4 - 15.29184/(-x2 + x3)</t>
+  </si>
+  <si>
+    <t>10**x1*x1*(-0.4981162)/(x2/0.2655104 + x3 + x8) - (-(0.7625352 - x4/2.3033595) + 20.147049/(-x2 + x3))</t>
+  </si>
+  <si>
+    <t>(Introducing parsimony related parameters to the model)</t>
+  </si>
+  <si>
+    <t>x3*0.029745026*10**x1 + x3*(-2.9628048)/(-x2 + x3) - (x1*x5 + x3*(-1.2491676)) - (x3 + x4*0.18625374 - 9.663681)</t>
+  </si>
+  <si>
+    <t>10**x1*x3*0.028684545 - x1*x5 - 19.472677/(-x2 + x3)</t>
+  </si>
+  <si>
+    <t>(x0*x1 + x4*(-0.26386178))/(x3*0.68185407 - (x0 - 0.66360754)) + (10**x0 + 10**x1)/10**(6.9349475/x3)</t>
+  </si>
+  <si>
+    <t>10**(x1 - 5.5316133/x3) + x1*(-0.62187374) - 19.101597/(-x2 + x3)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,6 +279,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFD4D4D4"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -127,10 +307,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -465,13 +648,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0FA0897-67B2-49BD-86B8-F0A88B8186F7}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="98.42578125" customWidth="1"/>
-    <col min="2" max="2" width="111" customWidth="1"/>
+    <col min="1" max="1" width="120" customWidth="1"/>
+    <col min="2" max="2" width="113.28515625" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="50.140625" customWidth="1"/>
+    <col min="4" max="4" width="75" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -501,7 +684,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -532,13 +715,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>0.44318125000000003</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5">
         <v>0.45788872000000003</v>
@@ -546,13 +729,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>0.43630326000000003</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6">
         <v>0.45792739999999998</v>
@@ -560,16 +743,402 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7">
         <v>0.4383666</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7">
         <v>0.45877384999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <v>0.43027583000000003</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8">
+        <v>0.45285540000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <v>0.42309454000000002</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9">
+        <v>0.45795763</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10">
+        <v>0.43989994999999998</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10">
+        <v>0.45648392999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11">
+        <v>0.42831599999999997</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11">
+        <v>0.44441589999999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12">
+        <v>0.43197744999999999</v>
+      </c>
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12">
+        <v>0.45878372000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13">
+        <v>0.42935960000000001</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13">
+        <v>0.45469619999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14">
+        <v>0.42520237</v>
+      </c>
+      <c r="D14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14">
+        <v>0.45297482999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16">
+        <v>0.43411174000000002</v>
+      </c>
+      <c r="D16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16">
+        <v>0.45796589999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17">
+        <v>0.41682156999999997</v>
+      </c>
+      <c r="D17" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17">
+        <v>0.45671405999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18">
+        <v>0.43016282</v>
+      </c>
+      <c r="D18" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18">
+        <v>0.45791754000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19">
+        <v>0.44343463</v>
+      </c>
+      <c r="D19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19">
+        <v>0.45788845</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20">
+        <v>0.44966233</v>
+      </c>
+      <c r="D20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20">
+        <v>0.45798680000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21">
+        <v>0.42483300000000002</v>
+      </c>
+      <c r="D21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21">
+        <v>0.47157442999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22">
+        <v>0.43925405000000001</v>
+      </c>
+      <c r="D22" t="s">
+        <v>65</v>
+      </c>
+      <c r="E22">
+        <v>0.44785580000000003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23">
+        <v>0.42666724</v>
+      </c>
+      <c r="D23" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23">
+        <v>0.44523442000000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25">
+        <v>0.39871780000000001</v>
+      </c>
+      <c r="D25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25">
+        <v>0.42231742</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26">
+        <v>0.39360875000000001</v>
+      </c>
+      <c r="D26" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26">
+        <v>0.40842511999999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27">
+        <v>0.39656462999999997</v>
+      </c>
+      <c r="D27" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27">
+        <v>0.44968851999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28">
+        <v>0.40663402999999998</v>
+      </c>
+      <c r="D28" t="s">
+        <v>49</v>
+      </c>
+      <c r="E28">
+        <v>0.43645676999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="3"/>
+      <c r="B29" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29">
+        <v>0.40338503999999997</v>
+      </c>
+      <c r="D29" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29">
+        <v>0.44970097999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="3"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31">
+        <v>0.51629990000000003</v>
+      </c>
+      <c r="D31" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31">
+        <v>0.54328759999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32">
+        <v>0.51906249999999998</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E32">
+        <v>0.54328626000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33">
+        <v>0.515926</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E33">
+        <v>0.52289430000000003</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35">
+        <v>0.47332210000000002</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E35">
+        <v>0.53724240000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36">
+        <v>0.49205821999999999</v>
+      </c>
+      <c r="D36" t="s">
+        <v>71</v>
+      </c>
+      <c r="E36">
+        <v>0.50380533999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37">
+        <v>0.49598663999999998</v>
+      </c>
+      <c r="D37" t="s">
+        <v>73</v>
+      </c>
+      <c r="E37">
+        <v>0.50211340000000004</v>
       </c>
     </row>
   </sheetData>

--- a/sr_past_runs.xlsx
+++ b/sr_past_runs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\reionisation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97669F9-7322-44D5-8C3B-F1C3E895DAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD8B924-4712-44C6-8264-25D5BB240C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="720" yWindow="3975" windowWidth="37155" windowHeight="15345" xr2:uid="{9831A600-CFBA-4EAE-B6C2-4EAF59100770}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
   <si>
     <t>Condition</t>
   </si>
@@ -258,6 +258,90 @@
   </si>
   <si>
     <t>10**(x1 - 5.5316133/x3) + x1*(-0.62187374) - 19.101597/(-x2 + x3)</t>
+  </si>
+  <si>
+    <t>10**x1*0.11301753 + 10**((-x0*x0 + x1)*0.18416542) + 10**((x0 + x1*0.296215 - 0.14578629)*0.296215) - 0.7379185*x2 + 92.90478</t>
+  </si>
+  <si>
+    <t>10**x1*0.13945632 - 10**(0.43002456 - 10**(x0*0.5477883)) - 0.7050375*x2 + 93.52721</t>
+  </si>
+  <si>
+    <t>x2*(-0.83123827) + exp((x0 + exp(x1))*(-0.10129792*x0 - 0.12063871*x1 + 0.58236784)) + exp(-x0 + x1)*0.00034942874 + 98.64395</t>
+  </si>
+  <si>
+    <t>-x2 + exp(x0*0.36527905 + x1*1.3003895) + 108.89195</t>
+  </si>
+  <si>
+    <t>x2*(-0.9354382) + (x2 - 1*56.94141)*(exp(x0) - 0.12690452)/1.3949735 + 104.69792 - 1.1716884/(x1 - 1.5593032)</t>
+  </si>
+  <si>
+    <t>x2*(-0.9331206) + exp(x0/2.479435 + x1*1.314263) + 104.88327</t>
+  </si>
+  <si>
+    <t>x0*(-0.9693696) + x0 - 0.8757647*x2 + (0.44569156 - (-0.052380048)*x0)*(x0 + 0.7247802)*(x1 - 1*(-1.2926697)) + exp(x1) + 101.40276</t>
+  </si>
+  <si>
+    <t>-x2 + exp(x0*0.36287922 + x1*1.2973721) + 108.8884</t>
+  </si>
+  <si>
+    <t>-0.8086302*x2 + (x0*1.4023628 + exp(x1))/exp(x0*(-0.25751013)) - exp(x0 - 0.14370383) + 98.95517</t>
+  </si>
+  <si>
+    <t>-x2 + exp(x0*0.36752224 + x1/0.76895183) + 108.893166</t>
+  </si>
+  <si>
+    <t>-x2 + exp(x0*0.36423594 + x1*1.291271) + 108.89835</t>
+  </si>
+  <si>
+    <t>x0 - (-5.7540336)*x0*x0/(x0 + x1 + x2) + x1*0.47437194*exp(x1) + x2*(-0.77479595) + 97.27663</t>
+  </si>
+  <si>
+    <t>-x2 + exp(x0/2.7513983 + x1*1.2936351) + 108.89542</t>
+  </si>
+  <si>
+    <t>x0*x0*x0*(-0.0015375862) - x2 + exp(x0/3.3366482 + x1 + 0.35027796) + 108.52458</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -x2 + exp(x0*0.36444497 + x1*1.2961153) + 108.89548</t>
+  </si>
+  <si>
+    <t>x2*8.726935e-6/exp(x0) + exp(x0*0.32101494 + x1 + 0.36017084) - 9.915395 - (-1)*3506.3574/x2</t>
+  </si>
+  <si>
+    <t>(nits = 500)</t>
+  </si>
+  <si>
+    <t>n_esc(obvs) - 3; batch_size: 4096, operators: {+, - , *, /, exp, log}, nan_indices:{gas_mass = 0}; pops: 100; pop_size: 100; nits: 100; maxd: 5</t>
+  </si>
+  <si>
+    <t>(x1 + 1.6777732)*x0*0.050247032 - (-2.1196065)*(x0 - 1*1.7171458)*exp(x0*0.8247181) + 5.5276737 - 30.343887/x1</t>
+  </si>
+  <si>
+    <t>-(1.4207463 - x0)*exp(x0) + 3.4349763 - 30.980812/x1</t>
+  </si>
+  <si>
+    <t>(-2.2119627*x0 + x1 - 15.383054)/(x0*x0 + x1/1.7690986) - (-(-0.17153157)*x0 - 0.2965434)/(1.6222788 + x1*(-0.3716915))</t>
+  </si>
+  <si>
+    <t>-113.3675*1/(x1*(-x0 + x1))</t>
+  </si>
+  <si>
+    <t>(-exp(x0) - 0.7232248/x1)/((x1/((-11.357486)*(x0 - 1*1.389013)))) - (x1 - 6.735734)/((x1/(-9.722194))*(x1 - exp(x0) - 1.1412327))</t>
+  </si>
+  <si>
+    <t>-113.357506*1/(x1*(-x0 + x1))</t>
+  </si>
+  <si>
+    <t>-0.080464266*x0*(-x0 + x2)/(x0*x0 - x1/x0) + x2*(-0.14882047)/(x1 - 1*2.766615) - exp(x0)/(x1 - 1*3.5621386)</t>
+  </si>
+  <si>
+    <t>113.36188/(x1*(x0 - x1))</t>
+  </si>
+  <si>
+    <t>(x0 - 1.4253812)*exp(x0) + 3.4257662 - 30.89592/x1</t>
+  </si>
+  <si>
+    <t>(-(-1.7154775)*x0 + x2*(-0.039403062))*(x1/x2 + exp(x0)) - (x1*0.2059149 - (x2*0.14103265 + 0.19432038) + 49.31989/x1)</t>
   </si>
 </sst>
 </file>
@@ -648,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0FA0897-67B2-49BD-86B8-F0A88B8186F7}">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="120" customWidth="1"/>
@@ -1141,6 +1225,194 @@
         <v>0.50211340000000004</v>
       </c>
     </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" t="s">
+        <v>74</v>
+      </c>
+      <c r="C41">
+        <v>0.46350851999999998</v>
+      </c>
+      <c r="D41" t="s">
+        <v>75</v>
+      </c>
+      <c r="E41">
+        <v>0.47065496000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>76</v>
+      </c>
+      <c r="C42">
+        <v>0.4304423</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E42">
+        <v>0.45431092000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>78</v>
+      </c>
+      <c r="C43">
+        <v>0.43983442</v>
+      </c>
+      <c r="D43" t="s">
+        <v>79</v>
+      </c>
+      <c r="E43">
+        <v>0.45309129999999997</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>80</v>
+      </c>
+      <c r="C44">
+        <v>0.43569079999999999</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E44">
+        <v>0.45431617000000002</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B45" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C45">
+        <v>0.43941910000000001</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E45">
+        <v>0.45432763999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>85</v>
+      </c>
+      <c r="C46">
+        <v>0.45431176000000001</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E46">
+        <v>0.45431176000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>87</v>
+      </c>
+      <c r="C47">
+        <v>0.44695016999999998</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E47">
+        <v>0.45430025000000002</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>90</v>
+      </c>
+      <c r="B48" t="s">
+        <v>89</v>
+      </c>
+      <c r="C48">
+        <v>0.44505674000000001</v>
+      </c>
+      <c r="D48" t="s">
+        <v>88</v>
+      </c>
+      <c r="E48">
+        <v>0.45429712999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>92</v>
+      </c>
+      <c r="C50">
+        <v>0.51549909999999999</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E50">
+        <v>0.52014773999999997</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>94</v>
+      </c>
+      <c r="C51">
+        <v>0.51562655000000002</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E51">
+        <v>0.53821269999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>96</v>
+      </c>
+      <c r="C52">
+        <v>0.51484160000000001</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E52">
+        <v>0.53821280000000005</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B53" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C53">
+        <v>0.51472910000000005</v>
+      </c>
+      <c r="D53" t="s">
+        <v>99</v>
+      </c>
+      <c r="E53">
+        <v>0.53821280000000005</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>101</v>
+      </c>
+      <c r="C54">
+        <v>0.51503104</v>
+      </c>
+      <c r="D54" t="s">
+        <v>100</v>
+      </c>
+      <c r="E54">
+        <v>0.52014059999999995</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
